--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728036</v>
+        <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>V fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484500</v>
+        <v>484843</v>
       </c>
       <c r="R2" t="n">
-        <v>7145888</v>
+        <v>7146089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,16 +786,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129728036</t>
+          <t>https://artportalen.se/Sighting/137373294</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129728061</v>
+        <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,38 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>V fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484833</v>
+        <v>484816</v>
       </c>
       <c r="R3" t="n">
-        <v>7146042</v>
+        <v>7146140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129728061</t>
+          <t>https://artportalen.se/Sighting/137373299</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130473092</v>
+        <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,45 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åviken, Fiskåtjärnen, Frostviken, Jmt</t>
+          <t>V fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484456</v>
+        <v>484875</v>
       </c>
       <c r="R4" t="n">
-        <v>7145887</v>
+        <v>7146073</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,17 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på gran.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,56 +995,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130473092</t>
+          <t>https://artportalen.se/Sighting/137373300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728055</v>
+        <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,46 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åviken, Jmt</t>
+          <t>V fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484520</v>
+        <v>484690</v>
       </c>
       <c r="R5" t="n">
-        <v>7145899</v>
+        <v>7146030</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,6 +1121,836 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373308</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129728036</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7145888</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728036</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129728061</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484833</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7146042</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728061</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130473092</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åviken, Fiskåtjärnen, Frostviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>484456</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7145887</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130473092</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137373298</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>V fiskåvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>484811</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7146149</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373298</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137373303</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>V fiskåvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>484860</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7146054</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373303</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137373307</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58034</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>V fiskåvattnet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>484582</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7145984</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373307</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129728055</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>484520</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7145899</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129728055</t>
         </is>
@@ -1160,6 +1962,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137373298</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137373303</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>137373307</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37565-2026 artfynd.xlsx
+++ b/artfynd/A 37565-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373294</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373299</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373300</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373308</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>137373298</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>137373303</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>137373307</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
